--- a/KZN Calendar 05 May 2026 -2026_2027.xlsx
+++ b/KZN Calendar 05 May 2026 -2026_2027.xlsx
@@ -184,9 +184,6 @@
     <t>National Women's Day</t>
   </si>
   <si>
-    <t>UDA District Gala</t>
-  </si>
-  <si>
     <t>Penguins</t>
   </si>
   <si>
@@ -647,6 +644,9 @@
   </si>
   <si>
     <t>Jolliffe Swimming Pool </t>
+  </si>
+  <si>
+    <t>UDA District Gala 2</t>
   </si>
 </sst>
 </file>
@@ -1111,14 +1111,6 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="177" fontId="26" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1127,6 +1119,14 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="datetime" xfId="1"/>
@@ -1331,7 +1331,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1376,7 +1376,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1411,8 +1411,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A9:G128">
-  <autoFilter ref="A9:G128"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A9:G127">
+  <autoFilter ref="A9:G127"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Event Name"/>
     <tableColumn id="2" name="Start Date"/>
@@ -1722,55 +1722,55 @@
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
     </row>
     <row r="2" spans="1:7" ht="24.9" customHeight="1">
-      <c r="B2" s="52"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
     </row>
     <row r="5" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A5" s="49" t="s">
-        <v>176</v>
-      </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
+      <c r="A5" s="55" t="s">
+        <v>175</v>
+      </c>
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2014,37 +2014,37 @@
       <c r="G16" s="11"/>
     </row>
     <row r="18" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A18" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="B18" s="50"/>
-      <c r="C18" s="50"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="50"/>
+      <c r="A18" s="55" t="s">
+        <v>183</v>
+      </c>
+      <c r="B18" s="54"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2293,37 +2293,37 @@
       <c r="G29" s="11"/>
     </row>
     <row r="31" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A31" s="49" t="s">
-        <v>185</v>
-      </c>
-      <c r="B31" s="50"/>
-      <c r="C31" s="50"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="50"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="50"/>
+      <c r="A31" s="55" t="s">
+        <v>184</v>
+      </c>
+      <c r="B31" s="54"/>
+      <c r="C31" s="54"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="54"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="54"/>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="C32" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="F32" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="G32" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2590,37 +2590,37 @@
       <c r="G44" s="11"/>
     </row>
     <row r="46" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A46" s="49" t="s">
-        <v>186</v>
-      </c>
-      <c r="B46" s="50"/>
-      <c r="C46" s="50"/>
-      <c r="D46" s="50"/>
-      <c r="E46" s="50"/>
-      <c r="F46" s="50"/>
-      <c r="G46" s="50"/>
+      <c r="A46" s="55" t="s">
+        <v>185</v>
+      </c>
+      <c r="B46" s="54"/>
+      <c r="C46" s="54"/>
+      <c r="D46" s="54"/>
+      <c r="E46" s="54"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="54"/>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="E47" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="F47" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="G47" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2864,37 +2864,37 @@
       <c r="G57" s="11"/>
     </row>
     <row r="59" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A59" s="49" t="s">
-        <v>187</v>
-      </c>
-      <c r="B59" s="50"/>
-      <c r="C59" s="50"/>
-      <c r="D59" s="50"/>
-      <c r="E59" s="50"/>
-      <c r="F59" s="50"/>
-      <c r="G59" s="50"/>
+      <c r="A59" s="55" t="s">
+        <v>186</v>
+      </c>
+      <c r="B59" s="54"/>
+      <c r="C59" s="54"/>
+      <c r="D59" s="54"/>
+      <c r="E59" s="54"/>
+      <c r="F59" s="54"/>
+      <c r="G59" s="54"/>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="C60" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="D60" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="E60" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="F60" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F60" s="2" t="s">
+      <c r="G60" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3143,37 +3143,37 @@
       <c r="G70" s="11"/>
     </row>
     <row r="72" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A72" s="49" t="s">
-        <v>188</v>
-      </c>
-      <c r="B72" s="50"/>
-      <c r="C72" s="50"/>
-      <c r="D72" s="50"/>
-      <c r="E72" s="50"/>
-      <c r="F72" s="50"/>
-      <c r="G72" s="50"/>
+      <c r="A72" s="55" t="s">
+        <v>187</v>
+      </c>
+      <c r="B72" s="54"/>
+      <c r="C72" s="54"/>
+      <c r="D72" s="54"/>
+      <c r="E72" s="54"/>
+      <c r="F72" s="54"/>
+      <c r="G72" s="54"/>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="C73" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="D73" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="E73" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E73" s="2" t="s">
+      <c r="F73" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F73" s="2" t="s">
+      <c r="G73" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3435,37 +3435,37 @@
       <c r="G85" s="11"/>
     </row>
     <row r="87" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A87" s="49" t="s">
-        <v>189</v>
-      </c>
-      <c r="B87" s="50"/>
-      <c r="C87" s="50"/>
-      <c r="D87" s="50"/>
-      <c r="E87" s="50"/>
-      <c r="F87" s="50"/>
-      <c r="G87" s="50"/>
+      <c r="A87" s="55" t="s">
+        <v>188</v>
+      </c>
+      <c r="B87" s="54"/>
+      <c r="C87" s="54"/>
+      <c r="D87" s="54"/>
+      <c r="E87" s="54"/>
+      <c r="F87" s="54"/>
+      <c r="G87" s="54"/>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="C88" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="D88" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="E88" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E88" s="2" t="s">
+      <c r="F88" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F88" s="2" t="s">
+      <c r="G88" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3714,37 +3714,37 @@
       <c r="G98" s="11"/>
     </row>
     <row r="100" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A100" s="49" t="s">
-        <v>190</v>
-      </c>
-      <c r="B100" s="50"/>
-      <c r="C100" s="50"/>
-      <c r="D100" s="50"/>
-      <c r="E100" s="50"/>
-      <c r="F100" s="50"/>
-      <c r="G100" s="50"/>
+      <c r="A100" s="55" t="s">
+        <v>189</v>
+      </c>
+      <c r="B100" s="54"/>
+      <c r="C100" s="54"/>
+      <c r="D100" s="54"/>
+      <c r="E100" s="54"/>
+      <c r="F100" s="54"/>
+      <c r="G100" s="54"/>
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="C101" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="D101" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D101" s="2" t="s">
+      <c r="E101" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E101" s="2" t="s">
+      <c r="F101" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F101" s="2" t="s">
+      <c r="G101" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3993,37 +3993,37 @@
       </c>
     </row>
     <row r="113" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A113" s="49" t="s">
-        <v>191</v>
-      </c>
-      <c r="B113" s="50"/>
-      <c r="C113" s="50"/>
-      <c r="D113" s="50"/>
-      <c r="E113" s="50"/>
-      <c r="F113" s="50"/>
-      <c r="G113" s="50"/>
+      <c r="A113" s="55" t="s">
+        <v>190</v>
+      </c>
+      <c r="B113" s="54"/>
+      <c r="C113" s="54"/>
+      <c r="D113" s="54"/>
+      <c r="E113" s="54"/>
+      <c r="F113" s="54"/>
+      <c r="G113" s="54"/>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B114" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="C114" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="D114" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D114" s="2" t="s">
+      <c r="E114" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E114" s="2" t="s">
+      <c r="F114" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F114" s="2" t="s">
+      <c r="G114" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="G114" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -4239,37 +4239,37 @@
       </c>
     </row>
     <row r="124" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A124" s="49" t="s">
-        <v>192</v>
-      </c>
-      <c r="B124" s="50"/>
-      <c r="C124" s="50"/>
-      <c r="D124" s="50"/>
-      <c r="E124" s="50"/>
-      <c r="F124" s="50"/>
-      <c r="G124" s="50"/>
+      <c r="A124" s="55" t="s">
+        <v>191</v>
+      </c>
+      <c r="B124" s="54"/>
+      <c r="C124" s="54"/>
+      <c r="D124" s="54"/>
+      <c r="E124" s="54"/>
+      <c r="F124" s="54"/>
+      <c r="G124" s="54"/>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="C125" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="D125" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D125" s="2" t="s">
+      <c r="E125" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E125" s="2" t="s">
+      <c r="F125" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F125" s="2" t="s">
+      <c r="G125" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="G125" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -4518,37 +4518,37 @@
       <c r="G135" s="11"/>
     </row>
     <row r="137" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A137" s="49" t="s">
-        <v>193</v>
-      </c>
-      <c r="B137" s="50"/>
-      <c r="C137" s="50"/>
-      <c r="D137" s="50"/>
-      <c r="E137" s="50"/>
-      <c r="F137" s="50"/>
-      <c r="G137" s="50"/>
+      <c r="A137" s="55" t="s">
+        <v>192</v>
+      </c>
+      <c r="B137" s="54"/>
+      <c r="C137" s="54"/>
+      <c r="D137" s="54"/>
+      <c r="E137" s="54"/>
+      <c r="F137" s="54"/>
+      <c r="G137" s="54"/>
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B138" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="C138" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C138" s="2" t="s">
+      <c r="D138" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D138" s="2" t="s">
+      <c r="E138" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E138" s="2" t="s">
+      <c r="F138" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F138" s="2" t="s">
+      <c r="G138" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="G138" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -4792,37 +4792,37 @@
       <c r="G148" s="11"/>
     </row>
     <row r="150" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A150" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="B150" s="50"/>
-      <c r="C150" s="50"/>
-      <c r="D150" s="50"/>
-      <c r="E150" s="50"/>
-      <c r="F150" s="50"/>
-      <c r="G150" s="50"/>
+      <c r="A150" s="55" t="s">
+        <v>193</v>
+      </c>
+      <c r="B150" s="54"/>
+      <c r="C150" s="54"/>
+      <c r="D150" s="54"/>
+      <c r="E150" s="54"/>
+      <c r="F150" s="54"/>
+      <c r="G150" s="54"/>
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B151" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="C151" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C151" s="2" t="s">
+      <c r="D151" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D151" s="2" t="s">
+      <c r="E151" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E151" s="2" t="s">
+      <c r="F151" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F151" s="2" t="s">
+      <c r="G151" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="G151" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -5090,6 +5090,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A150:G150"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A124:G124"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A137:G137"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="A100:G100"/>
     <mergeCell ref="A72:G72"/>
@@ -5098,12 +5104,6 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A46:G46"/>
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="A150:G150"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A124:G124"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A137:G137"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5112,7 +5112,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
@@ -5124,13 +5124,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
       <c r="G1" s="32"/>
     </row>
     <row r="2" spans="1:7" ht="24.9" customHeight="1">
@@ -5502,7 +5502,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="40" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B27" s="42">
         <v>46210</v>
@@ -5514,7 +5514,7 @@
         <v>28</v>
       </c>
       <c r="E27" s="40" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F27" s="40" t="s">
         <v>30</v>
@@ -5548,7 +5548,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="40" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B29" s="42">
         <v>46228</v>
@@ -5603,27 +5603,27 @@
       <c r="F31" s="41"/>
       <c r="G31" s="41"/>
     </row>
-    <row r="32" spans="1:7" s="54" customFormat="1" ht="16.8" customHeight="1">
-      <c r="A32" s="53" t="s">
+    <row r="32" spans="1:7" s="50" customFormat="1" ht="16.8" customHeight="1">
+      <c r="A32" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="B32" s="51" t="s">
         <v>201</v>
       </c>
-      <c r="B32" s="55" t="s">
+      <c r="C32" s="51" t="s">
         <v>202</v>
       </c>
-      <c r="C32" s="55" t="s">
+      <c r="D32" s="49" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32" s="49" t="s">
+        <v>39</v>
+      </c>
+      <c r="F32" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="G32" s="49" t="s">
         <v>203</v>
-      </c>
-      <c r="D32" s="53" t="s">
-        <v>39</v>
-      </c>
-      <c r="E32" s="53" t="s">
-        <v>39</v>
-      </c>
-      <c r="F32" s="53" t="s">
-        <v>30</v>
-      </c>
-      <c r="G32" s="53" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -5685,42 +5685,42 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="40" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B36" s="42">
         <v>46249</v>
       </c>
       <c r="C36" s="42">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="D36" s="40" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E36" s="40" t="s">
-        <v>43</v>
+        <v>196</v>
       </c>
       <c r="F36" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G36" s="40" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" s="45" customFormat="1">
       <c r="A37" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" s="42">
+        <v>46256</v>
+      </c>
+      <c r="C37" s="42">
+        <v>46257</v>
+      </c>
+      <c r="D37" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="B37" s="42">
-        <v>46249</v>
-      </c>
-      <c r="C37" s="42">
-        <v>46250</v>
-      </c>
-      <c r="D37" s="40" t="s">
-        <v>54</v>
-      </c>
       <c r="E37" s="40" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F37" s="40" t="s">
         <v>30</v>
@@ -5729,101 +5729,101 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:7" s="45" customFormat="1">
+    <row r="38" spans="1:7">
       <c r="A38" s="40" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B38" s="42">
-        <v>46256</v>
+        <v>46277</v>
       </c>
       <c r="C38" s="42">
-        <v>46257</v>
+        <v>46278</v>
       </c>
       <c r="D38" s="40" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E38" s="40" t="s">
-        <v>197</v>
+        <v>56</v>
       </c>
       <c r="F38" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G38" s="40" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="B39" s="42">
-        <v>46277</v>
-      </c>
-      <c r="C39" s="42">
-        <v>46278</v>
-      </c>
-      <c r="D39" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="E39" s="40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A39" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="F39" s="40" t="s">
+      <c r="B39" s="41"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="41"/>
+      <c r="G39" s="41"/>
+    </row>
+    <row r="40" spans="1:7" ht="24.9" customHeight="1">
+      <c r="A40" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="B40" s="42">
+        <v>46270</v>
+      </c>
+      <c r="C40" s="42">
+        <v>46270</v>
+      </c>
+      <c r="D40" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="E40" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="F40" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="G39" s="40" t="s">
+      <c r="G40" s="40" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A40" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="B40" s="41"/>
-      <c r="C40" s="41"/>
-      <c r="D40" s="41"/>
-      <c r="E40" s="41"/>
-      <c r="F40" s="41"/>
-      <c r="G40" s="41"/>
-    </row>
-    <row r="41" spans="1:7" ht="24.9" customHeight="1">
+    <row r="41" spans="1:7">
       <c r="A41" s="40" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B41" s="42">
         <v>46270</v>
       </c>
       <c r="C41" s="42">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="D41" s="40" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="E41" s="40" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="F41" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G41" s="40" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="40" t="s">
-        <v>62</v>
+        <v>205</v>
       </c>
       <c r="B42" s="42">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="C42" s="42">
-        <v>46271</v>
+        <v>46284</v>
       </c>
       <c r="D42" s="40" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E42" s="40" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F42" s="40" t="s">
         <v>30</v>
@@ -5834,7 +5834,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="40" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B43" s="42">
         <v>46285</v>
@@ -5843,10 +5843,10 @@
         <v>46285</v>
       </c>
       <c r="D43" s="40" t="s">
+        <v>63</v>
+      </c>
+      <c r="E43" s="40" t="s">
         <v>64</v>
-      </c>
-      <c r="E43" s="40" t="s">
-        <v>65</v>
       </c>
       <c r="F43" s="40" t="s">
         <v>30</v>
@@ -5857,7 +5857,7 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="40" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B44" s="42">
         <v>46289</v>
@@ -5866,10 +5866,10 @@
         <v>46292</v>
       </c>
       <c r="D44" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="E44" s="56" t="s">
-        <v>205</v>
+        <v>66</v>
+      </c>
+      <c r="E44" s="52" t="s">
+        <v>204</v>
       </c>
       <c r="F44" s="40" t="s">
         <v>30</v>
@@ -5880,7 +5880,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B45" s="42">
         <v>46289</v>
@@ -5895,21 +5895,44 @@
         <v>8</v>
       </c>
     </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="B46" s="42">
+        <v>46291</v>
+      </c>
+      <c r="C46" s="42">
+        <v>46291</v>
+      </c>
+      <c r="D46" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="E46" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="F46" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="G46" s="40" t="s">
+        <v>6</v>
+      </c>
+    </row>
     <row r="47" spans="1:7">
       <c r="A47" s="40" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B47" s="42">
         <v>46291</v>
       </c>
       <c r="C47" s="42">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="D47" s="40" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E47" s="40" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="F47" s="40" t="s">
         <v>30</v>
@@ -5918,89 +5941,89 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="40" t="s">
-        <v>75</v>
-      </c>
-      <c r="B48" s="42">
-        <v>46291</v>
-      </c>
-      <c r="C48" s="42">
-        <v>46293</v>
-      </c>
-      <c r="D48" s="40" t="s">
+    <row r="48" spans="1:7" ht="24.9" customHeight="1">
+      <c r="A48" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="E48" s="40" t="s">
-        <v>47</v>
-      </c>
-      <c r="F48" s="40" t="s">
+      <c r="B48" s="41"/>
+      <c r="C48" s="41"/>
+      <c r="D48" s="41"/>
+      <c r="E48" s="41"/>
+      <c r="F48" s="41"/>
+      <c r="G48" s="41"/>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="B49" s="42">
+        <v>46298</v>
+      </c>
+      <c r="C49" s="42">
+        <v>46298</v>
+      </c>
+      <c r="D49" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E49" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="F49" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="G48" s="40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="24.9" customHeight="1">
-      <c r="A49" s="41" t="s">
-        <v>77</v>
-      </c>
-      <c r="B49" s="41"/>
-      <c r="C49" s="41"/>
-      <c r="D49" s="41"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="41"/>
-      <c r="G49" s="41"/>
+      <c r="G49" s="40" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B50" s="42">
         <v>46298</v>
       </c>
       <c r="C50" s="42">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="D50" s="40" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="E50" s="40" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F50" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G50" s="40" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="40" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B51" s="42">
-        <v>46298</v>
+        <v>46312</v>
       </c>
       <c r="C51" s="42">
-        <v>46299</v>
+        <v>46312</v>
       </c>
       <c r="D51" s="40" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="E51" s="40" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F51" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G51" s="40" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="40" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B52" s="42">
         <v>46312</v>
@@ -6009,10 +6032,10 @@
         <v>46312</v>
       </c>
       <c r="D52" s="40" t="s">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="E52" s="40" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F52" s="40" t="s">
         <v>30</v>
@@ -6023,340 +6046,334 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="40" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B53" s="42">
-        <v>46312</v>
+        <v>46318</v>
       </c>
       <c r="C53" s="42">
-        <v>46312</v>
+        <v>46320</v>
       </c>
       <c r="D53" s="40" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E53" s="40" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F53" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G53" s="40" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="24.9" customHeight="1">
       <c r="A54" s="40" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B54" s="42">
-        <v>46318</v>
+        <v>46326</v>
       </c>
       <c r="C54" s="42">
-        <v>46320</v>
+        <v>46326</v>
       </c>
       <c r="D54" s="40" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="E54" s="40" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="F54" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G54" s="40" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A55" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="B55" s="41"/>
+      <c r="C55" s="41"/>
+      <c r="D55" s="41"/>
+      <c r="E55" s="41"/>
+      <c r="F55" s="41"/>
+      <c r="G55" s="41"/>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="B56" s="42">
+        <v>46332</v>
+      </c>
+      <c r="C56" s="42">
+        <v>46334</v>
+      </c>
+      <c r="D56" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E56" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="F56" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="G56" s="40" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" ht="24.9" customHeight="1">
-      <c r="A55" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="B55" s="42">
-        <v>46326</v>
-      </c>
-      <c r="C55" s="42">
-        <v>46326</v>
-      </c>
-      <c r="D55" s="40" t="s">
-        <v>79</v>
-      </c>
-      <c r="E55" s="40" t="s">
-        <v>74</v>
-      </c>
-      <c r="F55" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="G55" s="40" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A56" s="41" t="s">
-        <v>91</v>
-      </c>
-      <c r="B56" s="41"/>
-      <c r="C56" s="41"/>
-      <c r="D56" s="41"/>
-      <c r="E56" s="41"/>
-      <c r="F56" s="41"/>
-      <c r="G56" s="41"/>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="40" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="B57" s="42">
-        <v>46332</v>
+        <v>46333</v>
       </c>
       <c r="C57" s="42">
-        <v>46334</v>
+        <v>46333</v>
       </c>
       <c r="D57" s="40" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="E57" s="40" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="F57" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G57" s="40" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="40" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B58" s="42">
-        <v>46333</v>
+        <v>46340</v>
       </c>
       <c r="C58" s="42">
-        <v>46333</v>
+        <v>46341</v>
       </c>
       <c r="D58" s="40" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E58" s="40" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="F58" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G58" s="40" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="40" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B59" s="42">
-        <v>46340</v>
+        <v>46347</v>
       </c>
       <c r="C59" s="42">
-        <v>46341</v>
+        <v>46347</v>
       </c>
       <c r="D59" s="40" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="E59" s="40" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F59" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G59" s="40" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="40" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B60" s="42">
         <v>46347</v>
       </c>
       <c r="C60" s="42">
-        <v>46347</v>
+        <v>46348</v>
       </c>
       <c r="D60" s="40" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="E60" s="40" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F60" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G60" s="40" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="40" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B61" s="42">
-        <v>46347</v>
+        <v>46353</v>
       </c>
       <c r="C61" s="42">
-        <v>46348</v>
+        <v>46355</v>
       </c>
       <c r="D61" s="40" t="s">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="E61" s="40" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F61" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G61" s="40" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="24.9" customHeight="1">
       <c r="A62" s="40" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B62" s="42">
-        <v>46353</v>
+        <v>46354</v>
       </c>
       <c r="C62" s="42">
-        <v>46355</v>
+        <v>46354</v>
       </c>
       <c r="D62" s="40" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E62" s="40" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F62" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G62" s="40" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A63" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="B63" s="41"/>
+      <c r="C63" s="41"/>
+      <c r="D63" s="41"/>
+      <c r="E63" s="41"/>
+      <c r="F63" s="41"/>
+      <c r="G63" s="41"/>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="B64" s="42">
+        <v>46360</v>
+      </c>
+      <c r="C64" s="42">
+        <v>46361</v>
+      </c>
+      <c r="D64" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="E64" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="F64" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="G64" s="40" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" ht="24.9" customHeight="1">
-      <c r="A63" s="40" t="s">
-        <v>103</v>
-      </c>
-      <c r="B63" s="42">
-        <v>46354</v>
-      </c>
-      <c r="C63" s="42">
-        <v>46354</v>
-      </c>
-      <c r="D63" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="E63" s="40" t="s">
-        <v>86</v>
-      </c>
-      <c r="F63" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="G63" s="40" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A64" s="41" t="s">
-        <v>104</v>
-      </c>
-      <c r="B64" s="41"/>
-      <c r="C64" s="41"/>
-      <c r="D64" s="41"/>
-      <c r="E64" s="41"/>
-      <c r="F64" s="41"/>
-      <c r="G64" s="41"/>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="40" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B65" s="42">
-        <v>46360</v>
+        <v>46366</v>
       </c>
       <c r="C65" s="42">
-        <v>46361</v>
+        <v>46370</v>
       </c>
       <c r="D65" s="40" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E65" s="40" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F65" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G65" s="40" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="40" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B66" s="42">
-        <v>46366</v>
+        <v>46372</v>
       </c>
       <c r="C66" s="42">
-        <v>46370</v>
-      </c>
-      <c r="D66" s="40" t="s">
-        <v>108</v>
-      </c>
-      <c r="E66" s="40" t="s">
-        <v>81</v>
-      </c>
-      <c r="F66" s="40" t="s">
-        <v>30</v>
-      </c>
+        <v>46372</v>
+      </c>
+      <c r="D66" s="40"/>
+      <c r="E66" s="40"/>
+      <c r="F66" s="40"/>
       <c r="G66" s="40" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="40" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B67" s="42">
-        <v>46372</v>
+        <v>46375</v>
       </c>
       <c r="C67" s="42">
-        <v>46372</v>
-      </c>
-      <c r="D67" s="40"/>
-      <c r="E67" s="40"/>
-      <c r="F67" s="40"/>
+        <v>46376</v>
+      </c>
+      <c r="D67" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="E67" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="F67" s="40" t="s">
+        <v>30</v>
+      </c>
       <c r="G67" s="40" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="40" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B68" s="42">
-        <v>46375</v>
+        <v>46381</v>
       </c>
       <c r="C68" s="42">
-        <v>46376</v>
-      </c>
-      <c r="D68" s="40" t="s">
-        <v>95</v>
-      </c>
-      <c r="E68" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="F68" s="40" t="s">
-        <v>30</v>
-      </c>
+        <v>46381</v>
+      </c>
+      <c r="D68" s="40"/>
+      <c r="E68" s="40"/>
+      <c r="F68" s="40"/>
       <c r="G68" s="40" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -6364,10 +6381,10 @@
         <v>110</v>
       </c>
       <c r="B69" s="42">
-        <v>46381</v>
+        <v>46382</v>
       </c>
       <c r="C69" s="42">
-        <v>46381</v>
+        <v>46382</v>
       </c>
       <c r="D69" s="40"/>
       <c r="E69" s="40"/>
@@ -6376,72 +6393,78 @@
         <v>8</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
-      <c r="A70" s="40" t="s">
+    <row r="70" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A70" s="41" t="s">
         <v>111</v>
       </c>
-      <c r="B70" s="42">
-        <v>46382</v>
-      </c>
-      <c r="C70" s="42">
-        <v>46382</v>
-      </c>
-      <c r="D70" s="40"/>
-      <c r="E70" s="40"/>
-      <c r="F70" s="40"/>
-      <c r="G70" s="40" t="s">
+      <c r="B70" s="41"/>
+      <c r="C70" s="41"/>
+      <c r="D70" s="41"/>
+      <c r="E70" s="41"/>
+      <c r="F70" s="41"/>
+      <c r="G70" s="41"/>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="B71" s="42">
+        <v>46388</v>
+      </c>
+      <c r="C71" s="42">
+        <v>46388</v>
+      </c>
+      <c r="D71" s="40"/>
+      <c r="E71" s="40"/>
+      <c r="F71" s="40"/>
+      <c r="G71" s="40" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A71" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="B71" s="41"/>
-      <c r="C71" s="41"/>
-      <c r="D71" s="41"/>
-      <c r="E71" s="41"/>
-      <c r="F71" s="41"/>
-      <c r="G71" s="41"/>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="40" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="B72" s="42">
-        <v>46388</v>
+        <v>46395</v>
       </c>
       <c r="C72" s="42">
-        <v>46388</v>
-      </c>
-      <c r="D72" s="40"/>
-      <c r="E72" s="40"/>
-      <c r="F72" s="40"/>
+        <v>46396</v>
+      </c>
+      <c r="D72" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="E72" s="40" t="s">
+        <v>113</v>
+      </c>
+      <c r="F72" s="40" t="s">
+        <v>30</v>
+      </c>
       <c r="G72" s="40" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="40" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B73" s="42">
-        <v>46395</v>
+        <v>46403</v>
       </c>
       <c r="C73" s="42">
-        <v>46396</v>
+        <v>46404</v>
       </c>
       <c r="D73" s="40" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="E73" s="40" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="F73" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G73" s="40" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -6455,16 +6478,16 @@
         <v>46404</v>
       </c>
       <c r="D74" s="40" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="E74" s="40" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="F74" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G74" s="40" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -6475,19 +6498,19 @@
         <v>46403</v>
       </c>
       <c r="C75" s="42">
-        <v>46404</v>
+        <v>46403</v>
       </c>
       <c r="D75" s="40" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="E75" s="40" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F75" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G75" s="40" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -6501,21 +6524,21 @@
         <v>46403</v>
       </c>
       <c r="D76" s="40" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E76" s="40" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="F76" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G76" s="40" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="40" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B77" s="42">
         <v>46403</v>
@@ -6524,16 +6547,16 @@
         <v>46403</v>
       </c>
       <c r="D77" s="40" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="E77" s="40" t="s">
-        <v>119</v>
+        <v>43</v>
       </c>
       <c r="F77" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G77" s="40" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -6541,22 +6564,22 @@
         <v>120</v>
       </c>
       <c r="B78" s="42">
-        <v>46403</v>
+        <v>46396</v>
       </c>
       <c r="C78" s="42">
-        <v>46403</v>
+        <v>46397</v>
       </c>
       <c r="D78" s="40" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E78" s="40" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="F78" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G78" s="40" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -6564,85 +6587,85 @@
         <v>121</v>
       </c>
       <c r="B79" s="42">
-        <v>46396</v>
+        <v>46404</v>
       </c>
       <c r="C79" s="42">
-        <v>46397</v>
+        <v>46404</v>
       </c>
       <c r="D79" s="40" t="s">
-        <v>44</v>
+        <v>122</v>
       </c>
       <c r="E79" s="40" t="s">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="F79" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G79" s="40" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="24.9" customHeight="1">
       <c r="A80" s="40" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B80" s="42">
-        <v>46404</v>
+        <v>46410</v>
       </c>
       <c r="C80" s="42">
-        <v>46404</v>
+        <v>46410</v>
       </c>
       <c r="D80" s="40" t="s">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="E80" s="40" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F80" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G80" s="40" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="24.9" customHeight="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
       <c r="A81" s="40" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B81" s="42">
-        <v>46410</v>
+        <v>46411</v>
       </c>
       <c r="C81" s="42">
-        <v>46410</v>
+        <v>46411</v>
       </c>
       <c r="D81" s="40" t="s">
-        <v>60</v>
+        <v>127</v>
       </c>
       <c r="E81" s="40" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F81" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G81" s="40" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="40" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B82" s="42">
-        <v>46411</v>
+        <v>46415</v>
       </c>
       <c r="C82" s="42">
-        <v>46411</v>
+        <v>46415</v>
       </c>
       <c r="D82" s="40" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E82" s="40" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="F82" s="40" t="s">
         <v>30</v>
@@ -6653,19 +6676,19 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="40" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B83" s="42">
         <v>46415</v>
       </c>
       <c r="C83" s="42">
-        <v>46415</v>
+        <v>46417</v>
       </c>
       <c r="D83" s="40" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="E83" s="40" t="s">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="F83" s="40" t="s">
         <v>30</v>
@@ -6676,19 +6699,19 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="40" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B84" s="42">
-        <v>46415</v>
+        <v>46416</v>
       </c>
       <c r="C84" s="42">
-        <v>46417</v>
+        <v>46416</v>
       </c>
       <c r="D84" s="40" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="E84" s="40" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F84" s="40" t="s">
         <v>30</v>
@@ -6699,19 +6722,19 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="40" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B85" s="42">
         <v>46416</v>
       </c>
       <c r="C85" s="42">
-        <v>46416</v>
+        <v>46417</v>
       </c>
       <c r="D85" s="40" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E85" s="40" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F85" s="40" t="s">
         <v>30</v>
@@ -6720,130 +6743,130 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" ht="17.25" customHeight="1">
       <c r="A86" s="40" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B86" s="42">
         <v>46416</v>
       </c>
       <c r="C86" s="42">
-        <v>46417</v>
+        <v>46418</v>
       </c>
       <c r="D86" s="40" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E86" s="40" t="s">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="F86" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G86" s="40" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="17.25" customHeight="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="24.9" customHeight="1">
       <c r="A87" s="40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B87" s="42">
-        <v>46416</v>
+        <v>46417</v>
       </c>
       <c r="C87" s="42">
         <v>46418</v>
       </c>
       <c r="D87" s="40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E87" s="40" t="s">
-        <v>74</v>
+        <v>143</v>
       </c>
       <c r="F87" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G87" s="40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="24.9" customHeight="1">
-      <c r="A88" s="40" t="s">
-        <v>142</v>
-      </c>
-      <c r="B88" s="42">
-        <v>46417</v>
-      </c>
-      <c r="C88" s="42">
-        <v>46418</v>
-      </c>
-      <c r="D88" s="40" t="s">
-        <v>143</v>
-      </c>
-      <c r="E88" s="40" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="16.8">
+      <c r="A88" s="41" t="s">
         <v>144</v>
       </c>
-      <c r="F88" s="40" t="s">
+      <c r="B88" s="41"/>
+      <c r="C88" s="41"/>
+      <c r="D88" s="41"/>
+      <c r="E88" s="41"/>
+      <c r="F88" s="41"/>
+      <c r="G88" s="41"/>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" s="40" t="s">
+        <v>145</v>
+      </c>
+      <c r="B89" s="42">
+        <v>46422</v>
+      </c>
+      <c r="C89" s="42">
+        <v>46422</v>
+      </c>
+      <c r="D89" s="40" t="s">
+        <v>146</v>
+      </c>
+      <c r="E89" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="F89" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="G88" s="40" t="s">
+      <c r="G89" s="40" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" ht="16.8">
-      <c r="A89" s="41" t="s">
-        <v>145</v>
-      </c>
-      <c r="B89" s="41"/>
-      <c r="C89" s="41"/>
-      <c r="D89" s="41"/>
-      <c r="E89" s="41"/>
-      <c r="F89" s="41"/>
-      <c r="G89" s="41"/>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="40" t="s">
-        <v>146</v>
+        <v>45</v>
       </c>
       <c r="B90" s="42">
         <v>46422</v>
       </c>
       <c r="C90" s="42">
-        <v>46422</v>
+        <v>46423</v>
       </c>
       <c r="D90" s="40" t="s">
-        <v>147</v>
+        <v>46</v>
       </c>
       <c r="E90" s="40" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="F90" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G90" s="40" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="40" t="s">
-        <v>45</v>
+        <v>147</v>
       </c>
       <c r="B91" s="42">
-        <v>46422</v>
+        <v>46424</v>
       </c>
       <c r="C91" s="42">
-        <v>46423</v>
+        <v>46424</v>
       </c>
       <c r="D91" s="40" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="E91" s="40" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="F91" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G91" s="40" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -6854,19 +6877,19 @@
         <v>46424</v>
       </c>
       <c r="C92" s="42">
-        <v>46424</v>
+        <v>46425</v>
       </c>
       <c r="D92" s="40" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="E92" s="40" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F92" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G92" s="40" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -6874,22 +6897,22 @@
         <v>149</v>
       </c>
       <c r="B93" s="42">
-        <v>46424</v>
+        <v>46431</v>
       </c>
       <c r="C93" s="42">
-        <v>46425</v>
+        <v>46431</v>
       </c>
       <c r="D93" s="40" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="E93" s="40" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="F93" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G93" s="40" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -6900,113 +6923,113 @@
         <v>46431</v>
       </c>
       <c r="C94" s="42">
-        <v>46431</v>
+        <v>46432</v>
       </c>
       <c r="D94" s="40" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E94" s="40" t="s">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="F94" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G94" s="40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="17.25" customHeight="1">
       <c r="A95" s="40" t="s">
         <v>151</v>
       </c>
       <c r="B95" s="42">
-        <v>46431</v>
+        <v>46438</v>
       </c>
       <c r="C95" s="42">
-        <v>46432</v>
+        <v>46438</v>
       </c>
       <c r="D95" s="40" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="E95" s="40" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F95" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G95" s="40" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="17.25" customHeight="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
       <c r="A96" s="40" t="s">
         <v>152</v>
       </c>
       <c r="B96" s="42">
-        <v>46438</v>
+        <v>46445</v>
       </c>
       <c r="C96" s="42">
-        <v>46438</v>
+        <v>46446</v>
       </c>
       <c r="D96" s="40" t="s">
-        <v>85</v>
+        <v>153</v>
       </c>
       <c r="E96" s="40" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="F96" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G96" s="40" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7">
-      <c r="A97" s="40" t="s">
-        <v>153</v>
-      </c>
-      <c r="B97" s="42">
-        <v>46445</v>
-      </c>
-      <c r="C97" s="42">
-        <v>46446</v>
-      </c>
-      <c r="D97" s="40" t="s">
-        <v>154</v>
-      </c>
-      <c r="E97" s="40" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="16.8">
+      <c r="A97" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="F97" s="40" t="s">
+      <c r="B97" s="41"/>
+      <c r="C97" s="41"/>
+      <c r="D97" s="41"/>
+      <c r="E97" s="41"/>
+      <c r="F97" s="41"/>
+      <c r="G97" s="41"/>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="B98" s="42">
+        <v>46447</v>
+      </c>
+      <c r="C98" s="42">
+        <v>46447</v>
+      </c>
+      <c r="D98" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="E98" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="F98" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="G97" s="40" t="s">
+      <c r="G98" s="40" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" ht="16.8">
-      <c r="A98" s="41" t="s">
-        <v>156</v>
-      </c>
-      <c r="B98" s="41"/>
-      <c r="C98" s="41"/>
-      <c r="D98" s="41"/>
-      <c r="E98" s="41"/>
-      <c r="F98" s="41"/>
-      <c r="G98" s="41"/>
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="B99" s="42">
+        <v>46448</v>
+      </c>
+      <c r="C99" s="42">
+        <v>46448</v>
+      </c>
+      <c r="D99" s="40" t="s">
         <v>157</v>
-      </c>
-      <c r="B99" s="42">
-        <v>46447</v>
-      </c>
-      <c r="C99" s="42">
-        <v>46447</v>
-      </c>
-      <c r="D99" s="40" t="s">
-        <v>158</v>
       </c>
       <c r="E99" s="40" t="s">
         <v>47</v>
@@ -7023,13 +7046,13 @@
         <v>159</v>
       </c>
       <c r="B100" s="42">
-        <v>46448</v>
+        <v>46449</v>
       </c>
       <c r="C100" s="42">
-        <v>46448</v>
+        <v>46449</v>
       </c>
       <c r="D100" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E100" s="40" t="s">
         <v>47</v>
@@ -7046,13 +7069,13 @@
         <v>160</v>
       </c>
       <c r="B101" s="42">
-        <v>46449</v>
+        <v>46450</v>
       </c>
       <c r="C101" s="42">
-        <v>46449</v>
+        <v>46450</v>
       </c>
       <c r="D101" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E101" s="40" t="s">
         <v>47</v>
@@ -7064,61 +7087,55 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
-      <c r="A102" s="40" t="s">
+    <row r="102" spans="1:7" s="48" customFormat="1">
+      <c r="A102" s="46" t="s">
         <v>161</v>
       </c>
-      <c r="B102" s="42">
-        <v>46450</v>
-      </c>
-      <c r="C102" s="42">
-        <v>46450</v>
-      </c>
-      <c r="D102" s="40" t="s">
-        <v>158</v>
-      </c>
-      <c r="E102" s="40" t="s">
+      <c r="B102" s="47">
+        <v>46462</v>
+      </c>
+      <c r="C102" s="47">
+        <v>46464</v>
+      </c>
+      <c r="D102" s="46" t="s">
+        <v>162</v>
+      </c>
+      <c r="E102" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="F102" s="40" t="s">
+      <c r="F102" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="G102" s="40" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" s="48" customFormat="1">
-      <c r="A103" s="46" t="s">
-        <v>162</v>
-      </c>
-      <c r="B103" s="47">
-        <v>46462</v>
-      </c>
-      <c r="C103" s="47">
-        <v>46464</v>
-      </c>
-      <c r="D103" s="46" t="s">
-        <v>163</v>
-      </c>
-      <c r="E103" s="46" t="s">
-        <v>47</v>
-      </c>
-      <c r="F103" s="46" t="s">
-        <v>30</v>
-      </c>
-      <c r="G103" s="46" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" ht="13.2" customHeight="1">
+      <c r="G102" s="46" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="13.2" customHeight="1">
+      <c r="A103" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="B103" s="42">
+        <v>46467</v>
+      </c>
+      <c r="C103" s="42">
+        <v>46467</v>
+      </c>
+      <c r="D103" s="40"/>
+      <c r="E103" s="40"/>
+      <c r="F103" s="40"/>
+      <c r="G103" s="40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
       <c r="A104" s="40" t="s">
         <v>19</v>
       </c>
       <c r="B104" s="42">
-        <v>46467</v>
+        <v>46468</v>
       </c>
       <c r="C104" s="42">
-        <v>46467</v>
+        <v>46468</v>
       </c>
       <c r="D104" s="40"/>
       <c r="E104" s="40"/>
@@ -7127,15 +7144,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:7" ht="24.9" customHeight="1">
       <c r="A105" s="40" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B105" s="42">
-        <v>46468</v>
+        <v>46472</v>
       </c>
       <c r="C105" s="42">
-        <v>46468</v>
+        <v>46472</v>
       </c>
       <c r="D105" s="40"/>
       <c r="E105" s="40"/>
@@ -7144,15 +7161,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="24.9" customHeight="1">
+    <row r="106" spans="1:7" ht="17.25" customHeight="1">
       <c r="A106" s="40" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B106" s="42">
-        <v>46472</v>
+        <v>46475</v>
       </c>
       <c r="C106" s="42">
-        <v>46472</v>
+        <v>46475</v>
       </c>
       <c r="D106" s="40"/>
       <c r="E106" s="40"/>
@@ -7161,72 +7178,78 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="17.25" customHeight="1">
+    <row r="107" spans="1:7" ht="24.9" customHeight="1">
       <c r="A107" s="40" t="s">
-        <v>22</v>
+        <v>164</v>
       </c>
       <c r="B107" s="42">
-        <v>46475</v>
+        <v>46477</v>
       </c>
       <c r="C107" s="42">
-        <v>46475</v>
-      </c>
-      <c r="D107" s="40"/>
-      <c r="E107" s="40"/>
-      <c r="F107" s="40"/>
+        <v>46477</v>
+      </c>
+      <c r="D107" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="E107" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="F107" s="40" t="s">
+        <v>30</v>
+      </c>
       <c r="G107" s="40" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" ht="24.9" customHeight="1">
-      <c r="A108" s="40" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="16.8">
+      <c r="A108" s="41" t="s">
+        <v>166</v>
+      </c>
+      <c r="B108" s="41"/>
+      <c r="C108" s="41"/>
+      <c r="D108" s="41"/>
+      <c r="E108" s="41"/>
+      <c r="F108" s="41"/>
+      <c r="G108" s="41"/>
+    </row>
+    <row r="109" spans="1:7" ht="24.9" customHeight="1">
+      <c r="A109" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="B109" s="42">
+        <v>46478</v>
+      </c>
+      <c r="C109" s="42">
+        <v>46480</v>
+      </c>
+      <c r="D109" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="E109" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="B108" s="42">
-        <v>46477</v>
-      </c>
-      <c r="C108" s="42">
-        <v>46477</v>
-      </c>
-      <c r="D108" s="40" t="s">
-        <v>47</v>
-      </c>
-      <c r="E108" s="40" t="s">
-        <v>166</v>
-      </c>
-      <c r="F108" s="40" t="s">
+      <c r="F109" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="G108" s="40" t="s">
+      <c r="G109" s="40" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="16.8">
-      <c r="A109" s="41" t="s">
+    <row r="110" spans="1:7">
+      <c r="A110" s="40" t="s">
         <v>167</v>
       </c>
-      <c r="B109" s="41"/>
-      <c r="C109" s="41"/>
-      <c r="D109" s="41"/>
-      <c r="E109" s="41"/>
-      <c r="F109" s="41"/>
-      <c r="G109" s="41"/>
-    </row>
-    <row r="110" spans="1:7" ht="24.9" customHeight="1">
-      <c r="A110" s="40" t="s">
-        <v>165</v>
-      </c>
       <c r="B110" s="42">
-        <v>46478</v>
+        <v>46482</v>
       </c>
       <c r="C110" s="42">
-        <v>46480</v>
+        <v>46484</v>
       </c>
       <c r="D110" s="40" t="s">
         <v>47</v>
       </c>
       <c r="E110" s="40" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F110" s="40" t="s">
         <v>30</v>
@@ -7235,21 +7258,21 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" s="44" customFormat="1">
       <c r="A111" s="40" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B111" s="42">
-        <v>46482</v>
+        <v>46485</v>
       </c>
       <c r="C111" s="42">
-        <v>46484</v>
+        <v>46489</v>
       </c>
       <c r="D111" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="E111" s="40" t="s">
         <v>47</v>
-      </c>
-      <c r="E111" s="40" t="s">
-        <v>169</v>
       </c>
       <c r="F111" s="40" t="s">
         <v>30</v>
@@ -7258,18 +7281,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:7" s="44" customFormat="1">
+    <row r="112" spans="1:7" s="24" customFormat="1">
       <c r="A112" s="40" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B112" s="42">
-        <v>46485</v>
+        <v>46490</v>
       </c>
       <c r="C112" s="42">
-        <v>46489</v>
+        <v>46494</v>
       </c>
       <c r="D112" s="40" t="s">
-        <v>67</v>
+        <v>162</v>
       </c>
       <c r="E112" s="40" t="s">
         <v>47</v>
@@ -7281,18 +7304,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:7" s="24" customFormat="1">
+    <row r="113" spans="1:7" ht="13.2" customHeight="1">
       <c r="A113" s="40" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="B113" s="42">
-        <v>46490</v>
+        <v>46500</v>
       </c>
       <c r="C113" s="42">
-        <v>46494</v>
+        <v>46504</v>
       </c>
       <c r="D113" s="40" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="E113" s="40" t="s">
         <v>47</v>
@@ -7301,181 +7324,175 @@
         <v>30</v>
       </c>
       <c r="G113" s="40" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" ht="13.2" customHeight="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
       <c r="A114" s="40" t="s">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="B114" s="42">
-        <v>46500</v>
+        <v>46504</v>
       </c>
       <c r="C114" s="42">
         <v>46504</v>
       </c>
-      <c r="D114" s="40" t="s">
-        <v>196</v>
-      </c>
-      <c r="E114" s="40" t="s">
-        <v>47</v>
-      </c>
-      <c r="F114" s="40" t="s">
-        <v>30</v>
-      </c>
+      <c r="D114" s="40"/>
+      <c r="E114" s="40"/>
+      <c r="F114" s="40"/>
       <c r="G114" s="40" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7">
-      <c r="A115" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="B115" s="42">
-        <v>46504</v>
-      </c>
-      <c r="C115" s="42">
-        <v>46504</v>
-      </c>
-      <c r="D115" s="40"/>
-      <c r="E115" s="40"/>
-      <c r="F115" s="40"/>
-      <c r="G115" s="40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A116" s="41" t="s">
+    <row r="115" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A115" s="41" t="s">
+        <v>170</v>
+      </c>
+      <c r="B115" s="41"/>
+      <c r="C115" s="41"/>
+      <c r="D115" s="41"/>
+      <c r="E115" s="41"/>
+      <c r="F115" s="41"/>
+      <c r="G115" s="41"/>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B116" s="42">
+        <v>46508</v>
+      </c>
+      <c r="C116" s="42">
+        <v>46508</v>
+      </c>
+      <c r="D116" s="40"/>
+      <c r="E116" s="40"/>
+      <c r="F116" s="40"/>
+      <c r="G116" s="40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A117" s="41" t="s">
         <v>171</v>
       </c>
-      <c r="B116" s="41"/>
-      <c r="C116" s="41"/>
-      <c r="D116" s="41"/>
-      <c r="E116" s="41"/>
-      <c r="F116" s="41"/>
-      <c r="G116" s="41"/>
-    </row>
-    <row r="117" spans="1:7">
-      <c r="A117" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="B117" s="42">
-        <v>46508</v>
-      </c>
-      <c r="C117" s="42">
-        <v>46508</v>
-      </c>
-      <c r="D117" s="40"/>
-      <c r="E117" s="40"/>
-      <c r="F117" s="40"/>
-      <c r="G117" s="40" t="s">
+      <c r="B117" s="41"/>
+      <c r="C117" s="41"/>
+      <c r="D117" s="41"/>
+      <c r="E117" s="41"/>
+      <c r="F117" s="41"/>
+      <c r="G117" s="41"/>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="B118" s="42">
+        <v>46554</v>
+      </c>
+      <c r="C118" s="42">
+        <v>46554</v>
+      </c>
+      <c r="D118" s="40"/>
+      <c r="E118" s="40"/>
+      <c r="F118" s="40"/>
+      <c r="G118" s="40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A118" s="41" t="s">
+    <row r="119" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A119" s="41" t="s">
         <v>172</v>
       </c>
-      <c r="B118" s="41"/>
-      <c r="C118" s="41"/>
-      <c r="D118" s="41"/>
-      <c r="E118" s="41"/>
-      <c r="F118" s="41"/>
-      <c r="G118" s="41"/>
-    </row>
-    <row r="119" spans="1:7">
-      <c r="A119" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="B119" s="42">
-        <v>46554</v>
-      </c>
-      <c r="C119" s="42">
-        <v>46554</v>
-      </c>
-      <c r="D119" s="40"/>
-      <c r="E119" s="40"/>
-      <c r="F119" s="40"/>
-      <c r="G119" s="40" t="s">
+      <c r="B119" s="41"/>
+      <c r="C119" s="41"/>
+      <c r="D119" s="41"/>
+      <c r="E119" s="41"/>
+      <c r="F119" s="41"/>
+      <c r="G119" s="41"/>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="B120" s="42">
+        <v>46608</v>
+      </c>
+      <c r="C120" s="42">
+        <v>46608</v>
+      </c>
+      <c r="D120" s="40"/>
+      <c r="E120" s="40"/>
+      <c r="F120" s="40"/>
+      <c r="G120" s="40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A120" s="41" t="s">
+    <row r="121" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A121" s="41" t="s">
         <v>173</v>
       </c>
-      <c r="B120" s="41"/>
-      <c r="C120" s="41"/>
-      <c r="D120" s="41"/>
-      <c r="E120" s="41"/>
-      <c r="F120" s="41"/>
-      <c r="G120" s="41"/>
-    </row>
-    <row r="121" spans="1:7">
-      <c r="A121" s="40" t="s">
-        <v>50</v>
-      </c>
-      <c r="B121" s="42">
-        <v>46608</v>
-      </c>
-      <c r="C121" s="42">
-        <v>46608</v>
-      </c>
-      <c r="D121" s="40"/>
-      <c r="E121" s="40"/>
-      <c r="F121" s="40"/>
-      <c r="G121" s="40" t="s">
+      <c r="B121" s="41"/>
+      <c r="C121" s="41"/>
+      <c r="D121" s="41"/>
+      <c r="E121" s="41"/>
+      <c r="F121" s="41"/>
+      <c r="G121" s="41"/>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="B122" s="42">
+        <v>46654</v>
+      </c>
+      <c r="C122" s="42">
+        <v>46654</v>
+      </c>
+      <c r="D122" s="40"/>
+      <c r="E122" s="40"/>
+      <c r="F122" s="40"/>
+      <c r="G122" s="40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A122" s="41" t="s">
+    <row r="123" spans="1:7" ht="16.8">
+      <c r="A123" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="B122" s="41"/>
-      <c r="C122" s="41"/>
-      <c r="D122" s="41"/>
-      <c r="E122" s="41"/>
-      <c r="F122" s="41"/>
-      <c r="G122" s="41"/>
-    </row>
-    <row r="123" spans="1:7">
-      <c r="A123" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="B123" s="42">
-        <v>46654</v>
-      </c>
-      <c r="C123" s="42">
-        <v>46654</v>
-      </c>
-      <c r="D123" s="40"/>
-      <c r="E123" s="40"/>
-      <c r="F123" s="40"/>
-      <c r="G123" s="40" t="s">
+      <c r="B123" s="41"/>
+      <c r="C123" s="41"/>
+      <c r="D123" s="41"/>
+      <c r="E123" s="41"/>
+      <c r="F123" s="41"/>
+      <c r="G123" s="41"/>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="B124" s="42">
+        <v>46737</v>
+      </c>
+      <c r="C124" s="42">
+        <v>46737</v>
+      </c>
+      <c r="D124" s="40"/>
+      <c r="E124" s="40"/>
+      <c r="F124" s="40"/>
+      <c r="G124" s="40" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" ht="16.8">
-      <c r="A124" s="41" t="s">
-        <v>175</v>
-      </c>
-      <c r="B124" s="41"/>
-      <c r="C124" s="41"/>
-      <c r="D124" s="41"/>
-      <c r="E124" s="41"/>
-      <c r="F124" s="41"/>
-      <c r="G124" s="41"/>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="40" t="s">
         <v>109</v>
       </c>
       <c r="B125" s="42">
-        <v>46737</v>
+        <v>46746</v>
       </c>
       <c r="C125" s="42">
-        <v>46737</v>
+        <v>46746</v>
       </c>
       <c r="D125" s="40"/>
       <c r="E125" s="40"/>
@@ -7489,10 +7506,10 @@
         <v>110</v>
       </c>
       <c r="B126" s="42">
-        <v>46746</v>
+        <v>46747</v>
       </c>
       <c r="C126" s="42">
-        <v>46746</v>
+        <v>46747</v>
       </c>
       <c r="D126" s="40"/>
       <c r="E126" s="40"/>
@@ -7503,13 +7520,13 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="40" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B127" s="42">
-        <v>46747</v>
+        <v>46748</v>
       </c>
       <c r="C127" s="42">
-        <v>46747</v>
+        <v>46748</v>
       </c>
       <c r="D127" s="40"/>
       <c r="E127" s="40"/>
@@ -7518,28 +7535,11 @@
         <v>8</v>
       </c>
     </row>
-    <row r="128" spans="1:7">
-      <c r="A128" s="40" t="s">
-        <v>111</v>
-      </c>
-      <c r="B128" s="42">
-        <v>46748</v>
-      </c>
-      <c r="C128" s="42">
-        <v>46748</v>
-      </c>
-      <c r="D128" s="40"/>
-      <c r="E128" s="40"/>
-      <c r="F128" s="40"/>
-      <c r="G128" s="40" t="s">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A37:D37 G37:G38 E37:E38 A39:G43 A47:G128 A10:G36 A45:G45 A44:D44 F44:G44">
+  <conditionalFormatting sqref="A36:D36 G36:G37 E36:E37 A45:G127 A44:D44 F44:G44 A10:G35 A38:G43">
     <cfRule type="expression" dxfId="27" priority="29">
       <formula>$G10="National gala"</formula>
     </cfRule>
@@ -7562,77 +7562,77 @@
       <formula>$G10="Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A38:D38">
+  <conditionalFormatting sqref="A37:D37">
     <cfRule type="expression" dxfId="20" priority="15">
-      <formula>$G38="National gala"</formula>
+      <formula>$G37="National gala"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="16">
-      <formula>$G38="Provincial gala"</formula>
+      <formula>$G37="Provincial gala"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="18" priority="17">
-      <formula>$G38="District gala"</formula>
+      <formula>$G37="District gala"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="18">
-      <formula>$G38="Schools gala"</formula>
+      <formula>$G37="Schools gala"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="19">
-      <formula>$G38="Club gala"</formula>
+      <formula>$G37="Club gala"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="15" priority="20">
-      <formula>$G38="Open Water"</formula>
+      <formula>$G37="Open Water"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="21">
-      <formula>$G38="Public Holiday"</formula>
+      <formula>$G37="Public Holiday"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F36">
+    <cfRule type="expression" dxfId="13" priority="8">
+      <formula>$G36="National gala"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="9">
+      <formula>$G36="Provincial gala"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="10">
+      <formula>$G36="District gala"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="11">
+      <formula>$G36="Schools gala"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="12">
+      <formula>$G36="Club gala"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="13">
+      <formula>$G36="Open Water"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="14">
+      <formula>$G36="Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F37">
-    <cfRule type="expression" dxfId="13" priority="8">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>$G37="National gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="9">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>$G37="Provincial gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="10">
+    <cfRule type="expression" dxfId="4" priority="3">
       <formula>$G37="District gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="11">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>$G37="Schools gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="12">
+    <cfRule type="expression" dxfId="2" priority="5">
       <formula>$G37="Club gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="13">
+    <cfRule type="expression" dxfId="1" priority="6">
       <formula>$G37="Open Water"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="14">
+    <cfRule type="expression" dxfId="0" priority="7">
       <formula>$G37="Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F38">
-    <cfRule type="expression" dxfId="6" priority="1">
-      <formula>$G38="National gala"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="2">
-      <formula>$G38="Provincial gala"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="3">
-      <formula>$G38="District gala"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="4">
-      <formula>$G38="Schools gala"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="5">
-      <formula>$G38="Club gala"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="6">
-      <formula>$G38="Open Water"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="7">
-      <formula>$G38="Public Holiday"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="G47:G204 G2:G45">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G35 G36:G203">
       <formula1>"Club gala,District gala,Provincial gala,National gala,Open Water,Schools gala,Public Holiday"</formula1>
     </dataValidation>
   </dataValidations>

--- a/KZN Calendar 05 May 2026 -2026_2027.xlsx
+++ b/KZN Calendar 05 May 2026 -2026_2027.xlsx
@@ -1119,11 +1119,11 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1134,7 +1134,91 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="pro_day_only_🏊UnsanctionedCalendar" xfId="3"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="42">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9F1239"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC026D3"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF15803D"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFA16207"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7E22CE"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF0369A1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFEA580C"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9F1239"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC026D3"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF15803D"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFA16207"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7E22CE"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF0369A1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFEA580C"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1331,7 +1415,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1376,7 +1460,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1722,7 +1806,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="55" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="54"/>
@@ -1740,7 +1824,7 @@
       <c r="G2" s="54"/>
     </row>
     <row r="5" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="53" t="s">
         <v>175</v>
       </c>
       <c r="B5" s="54"/>
@@ -2014,7 +2098,7 @@
       <c r="G16" s="11"/>
     </row>
     <row r="18" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A18" s="55" t="s">
+      <c r="A18" s="53" t="s">
         <v>183</v>
       </c>
       <c r="B18" s="54"/>
@@ -2293,7 +2377,7 @@
       <c r="G29" s="11"/>
     </row>
     <row r="31" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A31" s="55" t="s">
+      <c r="A31" s="53" t="s">
         <v>184</v>
       </c>
       <c r="B31" s="54"/>
@@ -2590,7 +2674,7 @@
       <c r="G44" s="11"/>
     </row>
     <row r="46" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A46" s="55" t="s">
+      <c r="A46" s="53" t="s">
         <v>185</v>
       </c>
       <c r="B46" s="54"/>
@@ -2864,7 +2948,7 @@
       <c r="G57" s="11"/>
     </row>
     <row r="59" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A59" s="55" t="s">
+      <c r="A59" s="53" t="s">
         <v>186</v>
       </c>
       <c r="B59" s="54"/>
@@ -3143,7 +3227,7 @@
       <c r="G70" s="11"/>
     </row>
     <row r="72" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A72" s="55" t="s">
+      <c r="A72" s="53" t="s">
         <v>187</v>
       </c>
       <c r="B72" s="54"/>
@@ -3435,7 +3519,7 @@
       <c r="G85" s="11"/>
     </row>
     <row r="87" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A87" s="55" t="s">
+      <c r="A87" s="53" t="s">
         <v>188</v>
       </c>
       <c r="B87" s="54"/>
@@ -3714,7 +3798,7 @@
       <c r="G98" s="11"/>
     </row>
     <row r="100" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A100" s="55" t="s">
+      <c r="A100" s="53" t="s">
         <v>189</v>
       </c>
       <c r="B100" s="54"/>
@@ -3993,7 +4077,7 @@
       </c>
     </row>
     <row r="113" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A113" s="55" t="s">
+      <c r="A113" s="53" t="s">
         <v>190</v>
       </c>
       <c r="B113" s="54"/>
@@ -4239,7 +4323,7 @@
       </c>
     </row>
     <row r="124" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A124" s="55" t="s">
+      <c r="A124" s="53" t="s">
         <v>191</v>
       </c>
       <c r="B124" s="54"/>
@@ -4518,7 +4602,7 @@
       <c r="G135" s="11"/>
     </row>
     <row r="137" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A137" s="55" t="s">
+      <c r="A137" s="53" t="s">
         <v>192</v>
       </c>
       <c r="B137" s="54"/>
@@ -4792,7 +4876,7 @@
       <c r="G148" s="11"/>
     </row>
     <row r="150" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A150" s="55" t="s">
+      <c r="A150" s="53" t="s">
         <v>193</v>
       </c>
       <c r="B150" s="54"/>
@@ -5090,12 +5174,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A150:G150"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A124:G124"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A137:G137"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="A100:G100"/>
     <mergeCell ref="A72:G72"/>
@@ -5104,6 +5182,12 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A46:G46"/>
     <mergeCell ref="B2:G2"/>
+    <mergeCell ref="A150:G150"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A124:G124"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A137:G137"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5124,7 +5208,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="55" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="54"/>
@@ -5897,19 +5981,19 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="40" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B46" s="42">
         <v>46291</v>
       </c>
       <c r="C46" s="42">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="D46" s="40" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E46" s="40" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="F46" s="40" t="s">
         <v>30</v>
@@ -5918,84 +6002,84 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
-      <c r="A47" s="40" t="s">
-        <v>74</v>
-      </c>
-      <c r="B47" s="42">
-        <v>46291</v>
-      </c>
-      <c r="C47" s="42">
-        <v>46293</v>
-      </c>
-      <c r="D47" s="40" t="s">
-        <v>75</v>
-      </c>
-      <c r="E47" s="40" t="s">
-        <v>47</v>
-      </c>
-      <c r="F47" s="40" t="s">
+    <row r="47" spans="1:7" ht="24.9" customHeight="1">
+      <c r="A47" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="B47" s="41"/>
+      <c r="C47" s="41"/>
+      <c r="D47" s="41"/>
+      <c r="E47" s="41"/>
+      <c r="F47" s="41"/>
+      <c r="G47" s="41"/>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="B48" s="42">
+        <v>46298</v>
+      </c>
+      <c r="C48" s="42">
+        <v>46298</v>
+      </c>
+      <c r="D48" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E48" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="F48" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="G47" s="40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="24.9" customHeight="1">
-      <c r="A48" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="B48" s="41"/>
-      <c r="C48" s="41"/>
-      <c r="D48" s="41"/>
-      <c r="E48" s="41"/>
-      <c r="F48" s="41"/>
-      <c r="G48" s="41"/>
+      <c r="G48" s="40" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="40" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B49" s="42">
         <v>46298</v>
       </c>
       <c r="C49" s="42">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="D49" s="40" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="E49" s="40" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F49" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G49" s="40" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="40" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B50" s="42">
-        <v>46298</v>
+        <v>46312</v>
       </c>
       <c r="C50" s="42">
-        <v>46299</v>
+        <v>46312</v>
       </c>
       <c r="D50" s="40" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E50" s="40" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F50" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G50" s="40" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -6518,10 +6602,10 @@
         <v>117</v>
       </c>
       <c r="B76" s="42">
-        <v>46403</v>
+        <v>46404</v>
       </c>
       <c r="C76" s="42">
-        <v>46403</v>
+        <v>46404</v>
       </c>
       <c r="D76" s="40" t="s">
         <v>72</v>
@@ -7539,7 +7623,7 @@
   <mergeCells count="1">
     <mergeCell ref="B1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A36:D36 G36:G37 E36:E37 A45:G127 A44:D44 F44:G44 A10:G35 A38:G43">
+  <conditionalFormatting sqref="A36:D36 G36:G37 E36:E37 A44:D44 F44:G44 A10:G35 A38:G43 A45:G127">
     <cfRule type="expression" dxfId="27" priority="29">
       <formula>$G10="National gala"</formula>
     </cfRule>
@@ -7632,7 +7716,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="G2:G35 G36:G203">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G45 G46:G203">
       <formula1>"Club gala,District gala,Provincial gala,National gala,Open Water,Schools gala,Public Holiday"</formula1>
     </dataValidation>
   </dataValidations>

--- a/KZN Calendar 05 May 2026 -2026_2027.xlsx
+++ b/KZN Calendar 05 May 2026 -2026_2027.xlsx
@@ -1119,11 +1119,11 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1134,91 +1134,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="pro_day_only_🏊UnsanctionedCalendar" xfId="3"/>
   </cellStyles>
-  <dxfs count="42">
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9F1239"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFC026D3"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF15803D"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFA16207"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7E22CE"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF0369A1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFEA580C"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9F1239"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFC026D3"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF15803D"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFA16207"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7E22CE"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF0369A1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFEA580C"/>
-      </font>
-    </dxf>
+  <dxfs count="28">
     <dxf>
       <font>
         <b/>
@@ -1415,7 +1331,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1460,7 +1376,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1806,7 +1722,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="53" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="54"/>
@@ -1824,7 +1740,7 @@
       <c r="G2" s="54"/>
     </row>
     <row r="5" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="55" t="s">
         <v>175</v>
       </c>
       <c r="B5" s="54"/>
@@ -2098,7 +2014,7 @@
       <c r="G16" s="11"/>
     </row>
     <row r="18" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A18" s="53" t="s">
+      <c r="A18" s="55" t="s">
         <v>183</v>
       </c>
       <c r="B18" s="54"/>
@@ -2377,7 +2293,7 @@
       <c r="G29" s="11"/>
     </row>
     <row r="31" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A31" s="53" t="s">
+      <c r="A31" s="55" t="s">
         <v>184</v>
       </c>
       <c r="B31" s="54"/>
@@ -2674,7 +2590,7 @@
       <c r="G44" s="11"/>
     </row>
     <row r="46" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A46" s="53" t="s">
+      <c r="A46" s="55" t="s">
         <v>185</v>
       </c>
       <c r="B46" s="54"/>
@@ -2948,7 +2864,7 @@
       <c r="G57" s="11"/>
     </row>
     <row r="59" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A59" s="53" t="s">
+      <c r="A59" s="55" t="s">
         <v>186</v>
       </c>
       <c r="B59" s="54"/>
@@ -3227,7 +3143,7 @@
       <c r="G70" s="11"/>
     </row>
     <row r="72" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A72" s="53" t="s">
+      <c r="A72" s="55" t="s">
         <v>187</v>
       </c>
       <c r="B72" s="54"/>
@@ -3519,7 +3435,7 @@
       <c r="G85" s="11"/>
     </row>
     <row r="87" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A87" s="53" t="s">
+      <c r="A87" s="55" t="s">
         <v>188</v>
       </c>
       <c r="B87" s="54"/>
@@ -3798,7 +3714,7 @@
       <c r="G98" s="11"/>
     </row>
     <row r="100" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A100" s="53" t="s">
+      <c r="A100" s="55" t="s">
         <v>189</v>
       </c>
       <c r="B100" s="54"/>
@@ -4077,7 +3993,7 @@
       </c>
     </row>
     <row r="113" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A113" s="53" t="s">
+      <c r="A113" s="55" t="s">
         <v>190</v>
       </c>
       <c r="B113" s="54"/>
@@ -4323,7 +4239,7 @@
       </c>
     </row>
     <row r="124" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A124" s="53" t="s">
+      <c r="A124" s="55" t="s">
         <v>191</v>
       </c>
       <c r="B124" s="54"/>
@@ -4602,7 +4518,7 @@
       <c r="G135" s="11"/>
     </row>
     <row r="137" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A137" s="53" t="s">
+      <c r="A137" s="55" t="s">
         <v>192</v>
       </c>
       <c r="B137" s="54"/>
@@ -4876,7 +4792,7 @@
       <c r="G148" s="11"/>
     </row>
     <row r="150" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A150" s="53" t="s">
+      <c r="A150" s="55" t="s">
         <v>193</v>
       </c>
       <c r="B150" s="54"/>
@@ -5174,6 +5090,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A150:G150"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A124:G124"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A137:G137"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="A100:G100"/>
     <mergeCell ref="A72:G72"/>
@@ -5182,12 +5104,6 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A46:G46"/>
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="A150:G150"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A124:G124"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A137:G137"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5208,7 +5124,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="53" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="54"/>
@@ -6190,7 +6106,7 @@
         <v>68</v>
       </c>
       <c r="B56" s="42">
-        <v>46332</v>
+        <v>46333</v>
       </c>
       <c r="C56" s="42">
         <v>46334</v>
@@ -6233,152 +6149,152 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="40" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="B58" s="42">
+        <v>46339</v>
+      </c>
+      <c r="C58" s="42">
         <v>46340</v>
       </c>
-      <c r="C58" s="42">
-        <v>46341</v>
-      </c>
       <c r="D58" s="40" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="E58" s="40" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="F58" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G58" s="40" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="40" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B59" s="42">
-        <v>46347</v>
+        <v>46340</v>
       </c>
       <c r="C59" s="42">
-        <v>46347</v>
+        <v>46341</v>
       </c>
       <c r="D59" s="40" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="E59" s="40" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F59" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G59" s="40" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="40" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B60" s="42">
         <v>46347</v>
       </c>
       <c r="C60" s="42">
-        <v>46348</v>
+        <v>46347</v>
       </c>
       <c r="D60" s="40" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="E60" s="40" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F60" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G60" s="40" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="40" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B61" s="42">
-        <v>46353</v>
+        <v>46347</v>
       </c>
       <c r="C61" s="42">
-        <v>46355</v>
+        <v>46348</v>
       </c>
       <c r="D61" s="40" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="E61" s="40" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="F61" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G61" s="40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="24.9" customHeight="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
       <c r="A62" s="40" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B62" s="42">
-        <v>46354</v>
+        <v>46353</v>
       </c>
       <c r="C62" s="42">
-        <v>46354</v>
+        <v>46355</v>
       </c>
       <c r="D62" s="40" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="E62" s="40" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F62" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G62" s="40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="13.8" customHeight="1">
+      <c r="A63" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="B63" s="42">
+        <v>46354</v>
+      </c>
+      <c r="C63" s="42">
+        <v>46354</v>
+      </c>
+      <c r="D63" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="E63" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="F63" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="G63" s="40" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A63" s="41" t="s">
+    <row r="64" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A64" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="B63" s="41"/>
-      <c r="C63" s="41"/>
-      <c r="D63" s="41"/>
-      <c r="E63" s="41"/>
-      <c r="F63" s="41"/>
-      <c r="G63" s="41"/>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="B64" s="42">
-        <v>46360</v>
-      </c>
-      <c r="C64" s="42">
-        <v>46361</v>
-      </c>
-      <c r="D64" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="E64" s="40" t="s">
-        <v>73</v>
-      </c>
-      <c r="F64" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="G64" s="40" t="s">
-        <v>6</v>
-      </c>
+      <c r="B64" s="41"/>
+      <c r="C64" s="41"/>
+      <c r="D64" s="41"/>
+      <c r="E64" s="41"/>
+      <c r="F64" s="41"/>
+      <c r="G64" s="41"/>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="40" t="s">
@@ -6689,7 +6605,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="24.9" customHeight="1">
+    <row r="80" spans="1:7" ht="15.6" customHeight="1">
       <c r="A80" s="40" t="s">
         <v>124</v>
       </c>
@@ -7716,7 +7632,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="G2:G45 G46:G203">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G203">
       <formula1>"Club gala,District gala,Provincial gala,National gala,Open Water,Schools gala,Public Holiday"</formula1>
     </dataValidation>
   </dataValidations>
